--- a/metrics/terminal_recovery/物料名称表.xlsx
+++ b/metrics/terminal_recovery/物料名称表.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WPS\WPS Office\12.1.0.28505\office6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MonthlyReport\metrics\terminal_recovery\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="176">
   <si>
     <t>物料名称</t>
   </si>
@@ -667,6 +667,9 @@
   <si>
     <t>监控摄像头\球机\彩色高清\红外\千里眼E4702</t>
   </si>
+  <si>
+    <t>400万红外50米枪型网络摄像机GXX-IGU245(核算为其它部门成本)</t>
+  </si>
 </sst>
 </file>
 
@@ -678,7 +681,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -863,6 +866,11 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1369,7 +1377,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1390,7 +1398,7 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1929,14 +1937,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B168"/>
+  <dimension ref="A1:B169"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="90.1818181818182" customWidth="1"/>
     <col min="2" max="2" width="38.0909090909091" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="35" spans="1:2">
+    <row r="1" ht="17.5" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3271,6 +3279,14 @@
         <v>174</v>
       </c>
       <c r="B168" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B169" s="5" t="s">
         <v>33</v>
       </c>
     </row>
